--- a/data/Escenarios_DCH_septiembre/Bateria_353/Costo_fijo/Carga_on_board_fixed_3estaciones_P640kW/elmo_data.xlsx
+++ b/data/Escenarios_DCH_septiembre/Bateria_353/Costo_fijo/Carga_on_board_fixed_3estaciones_P640kW/elmo_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Escenarios_DCH_septiembre\Bateria_353\Costo_fijo\Carga_on_board_fixed_3estaciones_P640kW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB65634F-7C08-4C19-AEC7-FAFF3CE98F95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{386F133D-61D8-4C86-9285-FCE4E93C87AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3840" yWindow="3840" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AB3" s="32">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AC3" s="32">
-        <v>1</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="4" spans="1:75" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -2459,10 +2459,10 @@
         <v>0</v>
       </c>
       <c r="AB4" s="32">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AC4" s="32">
-        <v>1</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="5" spans="1:75" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="AB5" s="32">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AC5" s="32">
-        <v>1</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="6" spans="1:75" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -2637,10 +2637,10 @@
         <v>0</v>
       </c>
       <c r="AB6" s="32">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AC6" s="32">
-        <v>1</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="7" spans="1:75" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -2726,10 +2726,10 @@
         <v>0</v>
       </c>
       <c r="AB7" s="32">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AC7" s="32">
-        <v>1</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="8" spans="1:75" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -2815,10 +2815,10 @@
         <v>0</v>
       </c>
       <c r="AB8" s="32">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AC8" s="32">
-        <v>1</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="9" spans="1:75" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -2904,10 +2904,10 @@
         <v>0</v>
       </c>
       <c r="AB9" s="32">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AC9" s="32">
-        <v>1</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="10" spans="1:75" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -2993,10 +2993,10 @@
         <v>0</v>
       </c>
       <c r="AB10" s="32">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AC10" s="32">
-        <v>1</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="11" spans="1:75" s="32" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3082,10 +3082,10 @@
         <v>0</v>
       </c>
       <c r="AB11" s="32">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AC11" s="32">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AD11"/>
       <c r="AE11"/>
@@ -3217,10 +3217,10 @@
         <v>0</v>
       </c>
       <c r="AB12" s="32">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AC12" s="32">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AD12"/>
       <c r="AE12"/>
@@ -3352,10 +3352,10 @@
         <v>0</v>
       </c>
       <c r="AB13" s="32">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AC13" s="32">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AD13"/>
       <c r="AE13"/>
@@ -3487,10 +3487,10 @@
         <v>0</v>
       </c>
       <c r="AB14" s="32">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AC14" s="32">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="AD14"/>
       <c r="AE14"/>
